--- a/TeacherTraining/templates/master-certificateRecords-template.xlsx
+++ b/TeacherTraining/templates/master-certificateRecords-template.xlsx
@@ -90,7 +90,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-11</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
     </row>
